--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N103_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N103_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.93190125850755</v>
+        <v>9.901433954507477</v>
       </c>
       <c r="D2" t="n">
-        <v>61.34533716974658</v>
+        <v>9.96861729008382</v>
       </c>
       <c r="E2" t="n">
-        <v>12.49051636986751</v>
+        <v>2.029708910103471</v>
       </c>
       <c r="F2" t="n">
-        <v>12.21239964194678</v>
+        <v>1.984514941816352</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.42599579256788</v>
+        <v>8.519224316292281</v>
       </c>
       <c r="D3" t="n">
-        <v>51.44487116245013</v>
+        <v>8.359791563898145</v>
       </c>
       <c r="E3" t="n">
-        <v>12.49051636986751</v>
+        <v>2.029708910103471</v>
       </c>
       <c r="F3" t="n">
-        <v>12.21239964194678</v>
+        <v>1.984514941816352</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.97036716027479</v>
+        <v>7.145184663544653</v>
       </c>
       <c r="D4" t="n">
-        <v>44.89267480621976</v>
+        <v>7.295059656010711</v>
       </c>
       <c r="E4" t="n">
-        <v>12.49051636986751</v>
+        <v>2.029708910103471</v>
       </c>
       <c r="F4" t="n">
-        <v>12.21239964194678</v>
+        <v>1.984514941816352</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.28418392097034</v>
+        <v>9.146179887157679</v>
       </c>
       <c r="D5" t="n">
-        <v>55.34593589883296</v>
+        <v>8.993714583560356</v>
       </c>
       <c r="E5" t="n">
-        <v>12.49051636986751</v>
+        <v>2.029708910103471</v>
       </c>
       <c r="F5" t="n">
-        <v>12.21239964194678</v>
+        <v>1.984514941816352</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.27302415871963</v>
+        <v>3.45686642579194</v>
       </c>
       <c r="D6" t="n">
-        <v>22.24924741704658</v>
+        <v>3.615502705270069</v>
       </c>
       <c r="E6" t="n">
-        <v>12.49051636986751</v>
+        <v>2.029708910103471</v>
       </c>
       <c r="F6" t="n">
-        <v>12.21239964194678</v>
+        <v>1.984514941816352</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.42438930161724</v>
+        <v>6.731463261512801</v>
       </c>
       <c r="D7" t="n">
-        <v>42.42030034990044</v>
+        <v>6.893298806858821</v>
       </c>
       <c r="E7" t="n">
-        <v>12.49051636986751</v>
+        <v>2.029708910103471</v>
       </c>
       <c r="F7" t="n">
-        <v>12.21239964194678</v>
+        <v>1.984514941816352</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.98850035205251</v>
+        <v>6.823131307208533</v>
       </c>
       <c r="D8" t="n">
-        <v>42.92017575418282</v>
+        <v>6.974528560054709</v>
       </c>
       <c r="E8" t="n">
-        <v>12.49051636986751</v>
+        <v>2.029708910103471</v>
       </c>
       <c r="F8" t="n">
-        <v>12.21239964194678</v>
+        <v>1.984514941816352</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.32478914114674</v>
+        <v>5.252778235436345</v>
       </c>
       <c r="D9" t="n">
-        <v>32.23283048960048</v>
+        <v>5.237834954560078</v>
       </c>
       <c r="E9" t="n">
-        <v>12.49051636986751</v>
+        <v>2.029708910103471</v>
       </c>
       <c r="F9" t="n">
-        <v>12.21239964194678</v>
+        <v>1.984514941816352</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.21952951220869</v>
+        <v>6.048173545733912</v>
       </c>
       <c r="D10" t="n">
-        <v>37.65833531835688</v>
+        <v>6.119479489232993</v>
       </c>
       <c r="E10" t="n">
-        <v>12.49051636986751</v>
+        <v>2.029708910103471</v>
       </c>
       <c r="F10" t="n">
-        <v>12.21239964194678</v>
+        <v>1.984514941816352</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.38874929575864</v>
+        <v>3.800671760560778</v>
       </c>
       <c r="D11" t="n">
-        <v>23.57071069997402</v>
+        <v>3.830240488745778</v>
       </c>
       <c r="E11" t="n">
-        <v>12.49051636986751</v>
+        <v>2.029708910103471</v>
       </c>
       <c r="F11" t="n">
-        <v>12.21239964194678</v>
+        <v>1.984514941816352</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
